--- a/datosNivelesSin0Output.xlsx
+++ b/datosNivelesSin0Output.xlsx
@@ -4166,10 +4166,10 @@
         <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E67" t="n">
-        <v>-16213.918</v>
+        <v>982.155</v>
       </c>
       <c r="F67" t="n">
         <v>24</v>

--- a/datosNivelesSin0Output.xlsx
+++ b/datosNivelesSin0Output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R167"/>
+  <dimension ref="A1:T167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,16 @@
           <t>Num errores por tiempo excedido</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -570,6 +580,12 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="n">
+        <v>78.5714285714285</v>
+      </c>
+      <c r="T2" t="n">
+        <v>21.4285714285714</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -626,6 +642,12 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -682,6 +704,12 @@
       <c r="R4" t="n">
         <v>1</v>
       </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -737,6 +765,12 @@
       </c>
       <c r="R5" t="n">
         <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>77.7777777777777</v>
+      </c>
+      <c r="T5" t="n">
+        <v>22.2222222222222</v>
       </c>
     </row>
     <row r="6">
@@ -794,6 +828,12 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="n">
+        <v>80</v>
+      </c>
+      <c r="T6" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -849,6 +889,12 @@
       </c>
       <c r="R7" t="n">
         <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>90</v>
+      </c>
+      <c r="T7" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -906,6 +952,12 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="T8" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -962,6 +1014,12 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="n">
+        <v>77.7777777777777</v>
+      </c>
+      <c r="T9" t="n">
+        <v>22.2222222222222</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1018,6 +1076,12 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="n">
+        <v>100</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1074,6 +1138,12 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="T11" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1130,6 +1200,12 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1186,6 +1262,12 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1242,6 +1324,12 @@
       <c r="R14" t="n">
         <v>1</v>
       </c>
+      <c r="S14" t="n">
+        <v>75</v>
+      </c>
+      <c r="T14" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1298,6 +1386,12 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1354,6 +1448,12 @@
       <c r="R16" t="n">
         <v>1</v>
       </c>
+      <c r="S16" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1410,6 +1510,12 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="n">
+        <v>85.71428571428569</v>
+      </c>
+      <c r="T17" t="n">
+        <v>14.2857142857142</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1466,6 +1572,12 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1522,6 +1634,12 @@
       <c r="R19" t="n">
         <v>1</v>
       </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1578,6 +1696,12 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="n">
+        <v>100</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1634,6 +1758,12 @@
       <c r="R21" t="n">
         <v>1</v>
       </c>
+      <c r="S21" t="n">
+        <v>75</v>
+      </c>
+      <c r="T21" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1690,6 +1820,12 @@
       <c r="R22" t="n">
         <v>1</v>
       </c>
+      <c r="S22" t="n">
+        <v>100</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1746,6 +1882,12 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="n">
+        <v>100</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1802,6 +1944,12 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="n">
+        <v>100</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1858,6 +2006,12 @@
       <c r="R25" t="n">
         <v>1</v>
       </c>
+      <c r="S25" t="n">
+        <v>100</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1914,6 +2068,12 @@
       <c r="R26" t="n">
         <v>2</v>
       </c>
+      <c r="S26" t="n">
+        <v>100</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1970,6 +2130,12 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="n">
+        <v>75</v>
+      </c>
+      <c r="T27" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2026,6 +2192,12 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="n">
+        <v>94.4444444444444</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5.55555555555555</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2082,6 +2254,12 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="n">
+        <v>80</v>
+      </c>
+      <c r="T29" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2138,6 +2316,12 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="n">
+        <v>100</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2194,6 +2378,12 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="n">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="T31" t="n">
+        <v>11.1111111111111</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2250,6 +2440,12 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="n">
+        <v>100</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -2306,6 +2502,12 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="n">
+        <v>100</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -2362,6 +2564,12 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="n">
+        <v>76.4705882352941</v>
+      </c>
+      <c r="T34" t="n">
+        <v>23.5294117647058</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -2418,6 +2626,12 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="n">
+        <v>100</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2474,6 +2688,12 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="n">
+        <v>100</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2530,6 +2750,12 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="n">
+        <v>60</v>
+      </c>
+      <c r="T37" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -2586,6 +2812,12 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="T38" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -2642,6 +2874,12 @@
       <c r="R39" t="n">
         <v>1</v>
       </c>
+      <c r="S39" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="T39" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -2698,6 +2936,12 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="n">
+        <v>80</v>
+      </c>
+      <c r="T40" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -2754,6 +2998,12 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="n">
+        <v>76.92307692307691</v>
+      </c>
+      <c r="T41" t="n">
+        <v>23.076923076923</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -2810,6 +3060,12 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="n">
+        <v>100</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -2866,6 +3122,12 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="n">
+        <v>100</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -2922,6 +3184,12 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="n">
+        <v>100</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -2978,6 +3246,12 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="n">
+        <v>100</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -3034,6 +3308,12 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="n">
+        <v>85.71428571428569</v>
+      </c>
+      <c r="T46" t="n">
+        <v>14.2857142857142</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -3090,6 +3370,12 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="n">
+        <v>100</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -3146,6 +3432,12 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="n">
+        <v>75</v>
+      </c>
+      <c r="T48" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -3202,6 +3494,12 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="n">
+        <v>90.4761904761904</v>
+      </c>
+      <c r="T49" t="n">
+        <v>9.52380952380951</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -3258,6 +3556,12 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="n">
+        <v>100</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -3314,6 +3618,12 @@
       <c r="R51" t="n">
         <v>1</v>
       </c>
+      <c r="S51" t="n">
+        <v>86.6666666666666</v>
+      </c>
+      <c r="T51" t="n">
+        <v>13.3333333333333</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -3370,6 +3680,12 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="n">
+        <v>88.4615384615384</v>
+      </c>
+      <c r="T52" t="n">
+        <v>11.5384615384615</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -3426,6 +3742,12 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="n">
+        <v>100</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -3482,6 +3804,12 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="n">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="T54" t="n">
+        <v>11.1111111111111</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -3538,6 +3866,12 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="n">
+        <v>72.72727272727271</v>
+      </c>
+      <c r="T55" t="n">
+        <v>27.2727272727272</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -3594,6 +3928,12 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="n">
+        <v>93.9393939393939</v>
+      </c>
+      <c r="T56" t="n">
+        <v>6.06060606060606</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -3650,6 +3990,12 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="n">
+        <v>78.5714285714285</v>
+      </c>
+      <c r="T57" t="n">
+        <v>21.4285714285714</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -3706,6 +4052,12 @@
       <c r="R58" t="n">
         <v>3</v>
       </c>
+      <c r="S58" t="n">
+        <v>50</v>
+      </c>
+      <c r="T58" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -3762,6 +4114,12 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="n">
+        <v>73.68421052631579</v>
+      </c>
+      <c r="T59" t="n">
+        <v>26.3157894736842</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -3818,6 +4176,12 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="n">
+        <v>75</v>
+      </c>
+      <c r="T60" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -3874,6 +4238,12 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="T61" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -3930,6 +4300,12 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="n">
+        <v>90.90909090909091</v>
+      </c>
+      <c r="T62" t="n">
+        <v>9.09090909090909</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -3986,6 +4362,12 @@
       <c r="R63" t="n">
         <v>1</v>
       </c>
+      <c r="S63" t="n">
+        <v>100</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -4042,6 +4424,12 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
+      <c r="S64" t="n">
+        <v>100</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -4098,6 +4486,12 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="n">
+        <v>100</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -4154,6 +4548,12 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="n">
+        <v>94.4444444444444</v>
+      </c>
+      <c r="T66" t="n">
+        <v>5.55555555555555</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -4210,6 +4610,12 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
+      <c r="S67" t="n">
+        <v>79.1666666666666</v>
+      </c>
+      <c r="T67" t="n">
+        <v>20.8333333333333</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -4266,6 +4672,12 @@
       <c r="R68" t="n">
         <v>1</v>
       </c>
+      <c r="S68" t="n">
+        <v>100</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -4322,6 +4734,12 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="n">
+        <v>85.71428571428569</v>
+      </c>
+      <c r="T69" t="n">
+        <v>14.2857142857142</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -4378,6 +4796,12 @@
       <c r="R70" t="n">
         <v>2</v>
       </c>
+      <c r="S70" t="n">
+        <v>71.4285714285714</v>
+      </c>
+      <c r="T70" t="n">
+        <v>28.5714285714285</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -4434,6 +4858,12 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="n">
+        <v>60</v>
+      </c>
+      <c r="T71" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -4490,6 +4920,12 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
+      <c r="S72" t="n">
+        <v>100</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -4546,6 +4982,12 @@
       <c r="R73" t="n">
         <v>2</v>
       </c>
+      <c r="S73" t="n">
+        <v>100</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -4602,6 +5044,12 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="T74" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -4658,6 +5106,12 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="n">
+        <v>54.5454545454545</v>
+      </c>
+      <c r="T75" t="n">
+        <v>45.4545454545454</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -4714,6 +5168,12 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
+      <c r="S76" t="n">
+        <v>86.3636363636363</v>
+      </c>
+      <c r="T76" t="n">
+        <v>13.6363636363636</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -4770,6 +5230,12 @@
       <c r="R77" t="n">
         <v>1</v>
       </c>
+      <c r="S77" t="n">
+        <v>100</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -4826,6 +5292,12 @@
       <c r="R78" t="n">
         <v>0</v>
       </c>
+      <c r="S78" t="n">
+        <v>100</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -4882,6 +5354,12 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="n">
+        <v>100</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -4938,6 +5416,12 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
+      <c r="S80" t="n">
+        <v>71.4285714285714</v>
+      </c>
+      <c r="T80" t="n">
+        <v>28.5714285714285</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -4994,6 +5478,12 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
+      <c r="S81" t="n">
+        <v>80</v>
+      </c>
+      <c r="T81" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -5050,6 +5540,12 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
+      <c r="S82" t="n">
+        <v>100</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -5106,6 +5602,12 @@
       <c r="R83" t="n">
         <v>2</v>
       </c>
+      <c r="S83" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="T83" t="n">
+        <v>27.5</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -5162,6 +5664,12 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="n">
+        <v>80</v>
+      </c>
+      <c r="T84" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -5218,6 +5726,12 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="n">
+        <v>100</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -5274,6 +5788,12 @@
       <c r="R86" t="n">
         <v>3</v>
       </c>
+      <c r="S86" t="n">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="T86" t="n">
+        <v>11.1111111111111</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -5330,6 +5850,12 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="n">
+        <v>100</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -5386,6 +5912,12 @@
       <c r="R88" t="n">
         <v>3</v>
       </c>
+      <c r="S88" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="T88" t="n">
+        <v>18.75</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -5442,6 +5974,12 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
+      <c r="S89" t="n">
+        <v>92.30769230769231</v>
+      </c>
+      <c r="T89" t="n">
+        <v>7.69230769230769</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -5498,6 +6036,12 @@
       <c r="R90" t="n">
         <v>1</v>
       </c>
+      <c r="S90" t="n">
+        <v>86.6666666666666</v>
+      </c>
+      <c r="T90" t="n">
+        <v>13.3333333333333</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -5554,6 +6098,12 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="n">
+        <v>100</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -5610,6 +6160,12 @@
       <c r="R92" t="n">
         <v>0</v>
       </c>
+      <c r="S92" t="n">
+        <v>75</v>
+      </c>
+      <c r="T92" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -5666,6 +6222,12 @@
       <c r="R93" t="n">
         <v>0</v>
       </c>
+      <c r="S93" t="n">
+        <v>100</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -5722,6 +6284,12 @@
       <c r="R94" t="n">
         <v>0</v>
       </c>
+      <c r="S94" t="n">
+        <v>80</v>
+      </c>
+      <c r="T94" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -5778,6 +6346,12 @@
       <c r="R95" t="n">
         <v>1</v>
       </c>
+      <c r="S95" t="n">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="T95" t="n">
+        <v>11.1111111111111</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -5834,6 +6408,12 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="n">
+        <v>71.4285714285714</v>
+      </c>
+      <c r="T96" t="n">
+        <v>28.5714285714285</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -5890,6 +6470,12 @@
       <c r="R97" t="n">
         <v>1</v>
       </c>
+      <c r="S97" t="n">
+        <v>75</v>
+      </c>
+      <c r="T97" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -5946,6 +6532,12 @@
       <c r="R98" t="n">
         <v>0</v>
       </c>
+      <c r="S98" t="n">
+        <v>100</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -6002,6 +6594,12 @@
       <c r="R99" t="n">
         <v>0</v>
       </c>
+      <c r="S99" t="n">
+        <v>100</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -6058,6 +6656,12 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="n">
+        <v>100</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -6114,6 +6718,12 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
+      <c r="S101" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="T101" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -6170,6 +6780,12 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
+      <c r="S102" t="n">
+        <v>100</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -6226,6 +6842,12 @@
       <c r="R103" t="n">
         <v>1</v>
       </c>
+      <c r="S103" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="T103" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -6282,6 +6904,12 @@
       <c r="R104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="n">
+        <v>60</v>
+      </c>
+      <c r="T104" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -6338,6 +6966,12 @@
       <c r="R105" t="n">
         <v>0</v>
       </c>
+      <c r="S105" t="n">
+        <v>100</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -6394,6 +7028,12 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="T106" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -6450,6 +7090,12 @@
       <c r="R107" t="n">
         <v>2</v>
       </c>
+      <c r="S107" t="n">
+        <v>100</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -6506,6 +7152,12 @@
       <c r="R108" t="n">
         <v>0</v>
       </c>
+      <c r="S108" t="n">
+        <v>100</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -6562,6 +7214,12 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
+      <c r="S109" t="n">
+        <v>100</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -6618,6 +7276,12 @@
       <c r="R110" t="n">
         <v>0</v>
       </c>
+      <c r="S110" t="n">
+        <v>100</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -6674,6 +7338,12 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="n">
+        <v>75</v>
+      </c>
+      <c r="T111" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -6730,6 +7400,12 @@
       <c r="R112" t="n">
         <v>1</v>
       </c>
+      <c r="S112" t="n">
+        <v>100</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -6786,6 +7462,12 @@
       <c r="R113" t="n">
         <v>0</v>
       </c>
+      <c r="S113" t="n">
+        <v>78.5714285714285</v>
+      </c>
+      <c r="T113" t="n">
+        <v>21.4285714285714</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -6842,6 +7524,12 @@
       <c r="R114" t="n">
         <v>0</v>
       </c>
+      <c r="S114" t="n">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="T114" t="n">
+        <v>11.1111111111111</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -6898,6 +7586,12 @@
       <c r="R115" t="n">
         <v>0</v>
       </c>
+      <c r="S115" t="n">
+        <v>76.92307692307691</v>
+      </c>
+      <c r="T115" t="n">
+        <v>23.076923076923</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -6954,6 +7648,12 @@
       <c r="R116" t="n">
         <v>2</v>
       </c>
+      <c r="S116" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="T116" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -7010,6 +7710,12 @@
       <c r="R117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="n">
+        <v>78.5714285714285</v>
+      </c>
+      <c r="T117" t="n">
+        <v>21.4285714285714</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -7066,6 +7772,12 @@
       <c r="R118" t="n">
         <v>1</v>
       </c>
+      <c r="S118" t="n">
+        <v>100</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -7122,6 +7834,12 @@
       <c r="R119" t="n">
         <v>4</v>
       </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -7178,6 +7896,12 @@
       <c r="R120" t="n">
         <v>0</v>
       </c>
+      <c r="S120" t="n">
+        <v>85.71428571428569</v>
+      </c>
+      <c r="T120" t="n">
+        <v>14.2857142857142</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -7234,6 +7958,12 @@
       <c r="R121" t="n">
         <v>6</v>
       </c>
+      <c r="S121" t="n">
+        <v>93.3333333333333</v>
+      </c>
+      <c r="T121" t="n">
+        <v>6.66666666666667</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -7290,6 +8020,12 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="T122" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -7346,6 +8082,12 @@
       <c r="R123" t="n">
         <v>2</v>
       </c>
+      <c r="S123" t="n">
+        <v>75</v>
+      </c>
+      <c r="T123" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -7402,6 +8144,12 @@
       <c r="R124" t="n">
         <v>0</v>
       </c>
+      <c r="S124" t="n">
+        <v>100</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -7458,6 +8206,12 @@
       <c r="R125" t="n">
         <v>0</v>
       </c>
+      <c r="S125" t="n">
+        <v>35.7142857142857</v>
+      </c>
+      <c r="T125" t="n">
+        <v>64.28571428571421</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -7514,6 +8268,12 @@
       <c r="R126" t="n">
         <v>7</v>
       </c>
+      <c r="S126" t="n">
+        <v>61.1111111111111</v>
+      </c>
+      <c r="T126" t="n">
+        <v>38.8888888888888</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -7570,6 +8330,12 @@
       <c r="R127" t="n">
         <v>0</v>
       </c>
+      <c r="S127" t="n">
+        <v>100</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -7626,6 +8392,12 @@
       <c r="R128" t="n">
         <v>0</v>
       </c>
+      <c r="S128" t="n">
+        <v>100</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -7682,6 +8454,12 @@
       <c r="R129" t="n">
         <v>1</v>
       </c>
+      <c r="S129" t="n">
+        <v>100</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -7738,6 +8516,12 @@
       <c r="R130" t="n">
         <v>0</v>
       </c>
+      <c r="S130" t="n">
+        <v>75</v>
+      </c>
+      <c r="T130" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -7794,6 +8578,12 @@
       <c r="R131" t="n">
         <v>0</v>
       </c>
+      <c r="S131" t="n">
+        <v>69.5652173913043</v>
+      </c>
+      <c r="T131" t="n">
+        <v>30.4347826086956</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -7850,6 +8640,12 @@
       <c r="R132" t="n">
         <v>0</v>
       </c>
+      <c r="S132" t="n">
+        <v>85.71428571428569</v>
+      </c>
+      <c r="T132" t="n">
+        <v>14.2857142857142</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -7906,6 +8702,12 @@
       <c r="R133" t="n">
         <v>0</v>
       </c>
+      <c r="S133" t="n">
+        <v>93.54838709677411</v>
+      </c>
+      <c r="T133" t="n">
+        <v>6.4516129032258</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -7962,6 +8764,12 @@
       <c r="R134" t="n">
         <v>0</v>
       </c>
+      <c r="S134" t="n">
+        <v>51.6129032258064</v>
+      </c>
+      <c r="T134" t="n">
+        <v>48.3870967741935</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -8018,6 +8826,12 @@
       <c r="R135" t="n">
         <v>0</v>
       </c>
+      <c r="S135" t="n">
+        <v>100</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -8074,6 +8888,12 @@
       <c r="R136" t="n">
         <v>0</v>
       </c>
+      <c r="S136" t="n">
+        <v>100</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -8130,6 +8950,12 @@
       <c r="R137" t="n">
         <v>0</v>
       </c>
+      <c r="S137" t="n">
+        <v>77.7777777777777</v>
+      </c>
+      <c r="T137" t="n">
+        <v>22.2222222222222</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -8186,6 +9012,12 @@
       <c r="R138" t="n">
         <v>0</v>
       </c>
+      <c r="S138" t="n">
+        <v>100</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -8242,6 +9074,12 @@
       <c r="R139" t="n">
         <v>0</v>
       </c>
+      <c r="S139" t="n">
+        <v>100</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -8298,6 +9136,12 @@
       <c r="R140" t="n">
         <v>0</v>
       </c>
+      <c r="S140" t="n">
+        <v>90</v>
+      </c>
+      <c r="T140" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -8354,6 +9198,12 @@
       <c r="R141" t="n">
         <v>1</v>
       </c>
+      <c r="S141" t="n">
+        <v>100</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -8410,6 +9260,12 @@
       <c r="R142" t="n">
         <v>0</v>
       </c>
+      <c r="S142" t="n">
+        <v>88.235294117647</v>
+      </c>
+      <c r="T142" t="n">
+        <v>11.7647058823529</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -8466,6 +9322,12 @@
       <c r="R143" t="n">
         <v>0</v>
       </c>
+      <c r="S143" t="n">
+        <v>86.6666666666666</v>
+      </c>
+      <c r="T143" t="n">
+        <v>13.3333333333333</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -8522,6 +9384,12 @@
       <c r="R144" t="n">
         <v>0</v>
       </c>
+      <c r="S144" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="T144" t="n">
+        <v>18.75</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -8578,6 +9446,12 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
+      <c r="S145" t="n">
+        <v>100</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -8634,6 +9508,12 @@
       <c r="R146" t="n">
         <v>0</v>
       </c>
+      <c r="S146" t="n">
+        <v>100</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -8690,6 +9570,12 @@
       <c r="R147" t="n">
         <v>1</v>
       </c>
+      <c r="S147" t="n">
+        <v>40</v>
+      </c>
+      <c r="T147" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -8746,6 +9632,12 @@
       <c r="R148" t="n">
         <v>2</v>
       </c>
+      <c r="S148" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="T148" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -8802,6 +9694,12 @@
       <c r="R149" t="n">
         <v>0</v>
       </c>
+      <c r="S149" t="n">
+        <v>100</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -8858,6 +9756,12 @@
       <c r="R150" t="n">
         <v>0</v>
       </c>
+      <c r="S150" t="n">
+        <v>75</v>
+      </c>
+      <c r="T150" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -8914,6 +9818,12 @@
       <c r="R151" t="n">
         <v>0</v>
       </c>
+      <c r="S151" t="n">
+        <v>90.90909090909091</v>
+      </c>
+      <c r="T151" t="n">
+        <v>9.09090909090909</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -8970,6 +9880,12 @@
       <c r="R152" t="n">
         <v>1</v>
       </c>
+      <c r="S152" t="n">
+        <v>100</v>
+      </c>
+      <c r="T152" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -9026,6 +9942,12 @@
       <c r="R153" t="n">
         <v>0</v>
       </c>
+      <c r="S153" t="n">
+        <v>85.71428571428569</v>
+      </c>
+      <c r="T153" t="n">
+        <v>14.2857142857142</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -9082,6 +10004,12 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
+      <c r="S154" t="n">
+        <v>100</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -9138,6 +10066,12 @@
       <c r="R155" t="n">
         <v>0</v>
       </c>
+      <c r="S155" t="n">
+        <v>100</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -9194,6 +10128,12 @@
       <c r="R156" t="n">
         <v>0</v>
       </c>
+      <c r="S156" t="n">
+        <v>100</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -9250,6 +10190,12 @@
       <c r="R157" t="n">
         <v>0</v>
       </c>
+      <c r="S157" t="n">
+        <v>100</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -9306,6 +10252,12 @@
       <c r="R158" t="n">
         <v>1</v>
       </c>
+      <c r="S158" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="T158" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -9362,6 +10314,12 @@
       <c r="R159" t="n">
         <v>0</v>
       </c>
+      <c r="S159" t="n">
+        <v>75.8620689655172</v>
+      </c>
+      <c r="T159" t="n">
+        <v>24.1379310344827</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -9418,6 +10376,12 @@
       <c r="R160" t="n">
         <v>0</v>
       </c>
+      <c r="S160" t="n">
+        <v>71.4285714285714</v>
+      </c>
+      <c r="T160" t="n">
+        <v>28.5714285714285</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -9474,6 +10438,12 @@
       <c r="R161" t="n">
         <v>2</v>
       </c>
+      <c r="S161" t="n">
+        <v>76</v>
+      </c>
+      <c r="T161" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -9530,6 +10500,12 @@
       <c r="R162" t="n">
         <v>0</v>
       </c>
+      <c r="S162" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="T162" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -9586,6 +10562,12 @@
       <c r="R163" t="n">
         <v>0</v>
       </c>
+      <c r="S163" t="n">
+        <v>100</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -9642,6 +10624,12 @@
       <c r="R164" t="n">
         <v>0</v>
       </c>
+      <c r="S164" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="T164" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -9698,6 +10686,12 @@
       <c r="R165" t="n">
         <v>0</v>
       </c>
+      <c r="S165" t="n">
+        <v>64.28571428571421</v>
+      </c>
+      <c r="T165" t="n">
+        <v>35.7142857142857</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -9754,6 +10748,12 @@
       <c r="R166" t="n">
         <v>0</v>
       </c>
+      <c r="S166" t="n">
+        <v>100</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -9809,6 +10809,12 @@
       </c>
       <c r="R167" t="n">
         <v>0</v>
+      </c>
+      <c r="S167" t="n">
+        <v>82.35294117647059</v>
+      </c>
+      <c r="T167" t="n">
+        <v>17.6470588235294</v>
       </c>
     </row>
   </sheetData>
